--- a/src/test/resources/data/Balance_Sheet_1787924075343.xlsx
+++ b/src/test/resources/data/Balance_Sheet_1787924075343.xlsx
@@ -1,18 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\towhid.islam\IdeaProjects\JFoundationKit\src\test\resources\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC4CA80-A5CA-46D8-BB46-871BADC6FC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-56460" yWindow="1140" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="data" r:id="rId3" sheetId="1"/>
+    <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="32">
   <si>
     <t>AccountName</t>
   </si>
@@ -113,13 +121,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -129,7 +136,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -147,24 +154,352 @@
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G101"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.70703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="9.078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="8.27734375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="8.02734375" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="11.1171875" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="24.14453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="19.8984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -187,7 +522,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -210,7 +545,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -233,7 +568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -256,7 +591,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -279,7 +614,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -302,7 +637,2192 @@
         <v>31</v>
       </c>
     </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" t="s">
+        <v>17</v>
+      </c>
+      <c r="G26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>28</v>
+      </c>
+      <c r="D35" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" t="s">
+        <v>21</v>
+      </c>
+      <c r="F35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>14</v>
+      </c>
+      <c r="D37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" t="s">
+        <v>21</v>
+      </c>
+      <c r="F39" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" t="s">
+        <v>29</v>
+      </c>
+      <c r="E41" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" t="s">
+        <v>21</v>
+      </c>
+      <c r="F44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" t="s">
+        <v>21</v>
+      </c>
+      <c r="F45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" t="s">
+        <v>28</v>
+      </c>
+      <c r="D46" t="s">
+        <v>29</v>
+      </c>
+      <c r="E46" t="s">
+        <v>21</v>
+      </c>
+      <c r="F46" t="s">
+        <v>30</v>
+      </c>
+      <c r="G46" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" t="s">
+        <v>12</v>
+      </c>
+      <c r="G47" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" t="s">
+        <v>17</v>
+      </c>
+      <c r="G48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" t="s">
+        <v>21</v>
+      </c>
+      <c r="F49" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" t="s">
+        <v>20</v>
+      </c>
+      <c r="E50" t="s">
+        <v>21</v>
+      </c>
+      <c r="F50" t="s">
+        <v>22</v>
+      </c>
+      <c r="G50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" t="s">
+        <v>29</v>
+      </c>
+      <c r="E52" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" t="s">
+        <v>30</v>
+      </c>
+      <c r="G52" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" t="s">
+        <v>17</v>
+      </c>
+      <c r="G54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" t="s">
+        <v>21</v>
+      </c>
+      <c r="F55" t="s">
+        <v>22</v>
+      </c>
+      <c r="G55" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" t="s">
+        <v>21</v>
+      </c>
+      <c r="F56" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57" t="s">
+        <v>30</v>
+      </c>
+      <c r="G57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59" t="s">
+        <v>17</v>
+      </c>
+      <c r="G59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" t="s">
+        <v>21</v>
+      </c>
+      <c r="F60" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" t="s">
+        <v>21</v>
+      </c>
+      <c r="F61" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" t="s">
+        <v>25</v>
+      </c>
+      <c r="E62" t="s">
+        <v>21</v>
+      </c>
+      <c r="F62" t="s">
+        <v>26</v>
+      </c>
+      <c r="G62" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" t="s">
+        <v>8</v>
+      </c>
+      <c r="C63" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" t="s">
+        <v>21</v>
+      </c>
+      <c r="F63" t="s">
+        <v>30</v>
+      </c>
+      <c r="G63" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" t="s">
+        <v>8</v>
+      </c>
+      <c r="C64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" t="s">
+        <v>12</v>
+      </c>
+      <c r="G64" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" t="s">
+        <v>15</v>
+      </c>
+      <c r="E65" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" t="s">
+        <v>8</v>
+      </c>
+      <c r="C66" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" t="s">
+        <v>21</v>
+      </c>
+      <c r="F67" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" t="s">
+        <v>29</v>
+      </c>
+      <c r="E68" t="s">
+        <v>21</v>
+      </c>
+      <c r="F68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G68" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" t="s">
+        <v>8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" t="s">
+        <v>12</v>
+      </c>
+      <c r="G69" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" t="s">
+        <v>15</v>
+      </c>
+      <c r="E70" t="s">
+        <v>16</v>
+      </c>
+      <c r="F70" t="s">
+        <v>17</v>
+      </c>
+      <c r="G70" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" t="s">
+        <v>21</v>
+      </c>
+      <c r="F71" t="s">
+        <v>22</v>
+      </c>
+      <c r="G71" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" t="s">
+        <v>15</v>
+      </c>
+      <c r="E72" t="s">
+        <v>16</v>
+      </c>
+      <c r="F72" t="s">
+        <v>17</v>
+      </c>
+      <c r="G72" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" t="s">
+        <v>21</v>
+      </c>
+      <c r="F73" t="s">
+        <v>22</v>
+      </c>
+      <c r="G73" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" t="s">
+        <v>21</v>
+      </c>
+      <c r="F74" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" t="s">
+        <v>28</v>
+      </c>
+      <c r="D75" t="s">
+        <v>29</v>
+      </c>
+      <c r="E75" t="s">
+        <v>21</v>
+      </c>
+      <c r="F75" t="s">
+        <v>30</v>
+      </c>
+      <c r="G75" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>7</v>
+      </c>
+      <c r="B76" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" t="s">
+        <v>12</v>
+      </c>
+      <c r="G76" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" t="s">
+        <v>16</v>
+      </c>
+      <c r="F77" t="s">
+        <v>17</v>
+      </c>
+      <c r="G77" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" t="s">
+        <v>22</v>
+      </c>
+      <c r="G78" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" t="s">
+        <v>19</v>
+      </c>
+      <c r="D79" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" t="s">
+        <v>21</v>
+      </c>
+      <c r="F79" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80" t="s">
+        <v>25</v>
+      </c>
+      <c r="E80" t="s">
+        <v>21</v>
+      </c>
+      <c r="F80" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>7</v>
+      </c>
+      <c r="B81" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" t="s">
+        <v>28</v>
+      </c>
+      <c r="D81" t="s">
+        <v>29</v>
+      </c>
+      <c r="E81" t="s">
+        <v>21</v>
+      </c>
+      <c r="F81" t="s">
+        <v>30</v>
+      </c>
+      <c r="G81" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" t="s">
+        <v>12</v>
+      </c>
+      <c r="G82" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" t="s">
+        <v>14</v>
+      </c>
+      <c r="D83" t="s">
+        <v>15</v>
+      </c>
+      <c r="E83" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" t="s">
+        <v>17</v>
+      </c>
+      <c r="G83" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" t="s">
+        <v>20</v>
+      </c>
+      <c r="E84" t="s">
+        <v>21</v>
+      </c>
+      <c r="F84" t="s">
+        <v>22</v>
+      </c>
+      <c r="G84" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" t="s">
+        <v>24</v>
+      </c>
+      <c r="D85" t="s">
+        <v>25</v>
+      </c>
+      <c r="E85" t="s">
+        <v>21</v>
+      </c>
+      <c r="F85" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" t="s">
+        <v>28</v>
+      </c>
+      <c r="D86" t="s">
+        <v>29</v>
+      </c>
+      <c r="E86" t="s">
+        <v>21</v>
+      </c>
+      <c r="F86" t="s">
+        <v>30</v>
+      </c>
+      <c r="G86" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" t="s">
+        <v>15</v>
+      </c>
+      <c r="E87" t="s">
+        <v>16</v>
+      </c>
+      <c r="F87" t="s">
+        <v>17</v>
+      </c>
+      <c r="G87" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>7</v>
+      </c>
+      <c r="B88" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" t="s">
+        <v>19</v>
+      </c>
+      <c r="D88" t="s">
+        <v>20</v>
+      </c>
+      <c r="E88" t="s">
+        <v>21</v>
+      </c>
+      <c r="F88" t="s">
+        <v>22</v>
+      </c>
+      <c r="G88" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>7</v>
+      </c>
+      <c r="B89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" t="s">
+        <v>24</v>
+      </c>
+      <c r="D89" t="s">
+        <v>25</v>
+      </c>
+      <c r="E89" t="s">
+        <v>21</v>
+      </c>
+      <c r="F89" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" t="s">
+        <v>28</v>
+      </c>
+      <c r="D90" t="s">
+        <v>29</v>
+      </c>
+      <c r="E90" t="s">
+        <v>21</v>
+      </c>
+      <c r="F90" t="s">
+        <v>30</v>
+      </c>
+      <c r="G90" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>7</v>
+      </c>
+      <c r="B92" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" t="s">
+        <v>14</v>
+      </c>
+      <c r="D92" t="s">
+        <v>15</v>
+      </c>
+      <c r="E92" t="s">
+        <v>16</v>
+      </c>
+      <c r="F92" t="s">
+        <v>17</v>
+      </c>
+      <c r="G92" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>7</v>
+      </c>
+      <c r="B93" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" t="s">
+        <v>19</v>
+      </c>
+      <c r="D93" t="s">
+        <v>20</v>
+      </c>
+      <c r="E93" t="s">
+        <v>21</v>
+      </c>
+      <c r="F93" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>7</v>
+      </c>
+      <c r="B94" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" t="s">
+        <v>19</v>
+      </c>
+      <c r="D94" t="s">
+        <v>20</v>
+      </c>
+      <c r="E94" t="s">
+        <v>21</v>
+      </c>
+      <c r="F94" t="s">
+        <v>22</v>
+      </c>
+      <c r="G94" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>7</v>
+      </c>
+      <c r="B95" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" t="s">
+        <v>24</v>
+      </c>
+      <c r="D95" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" t="s">
+        <v>21</v>
+      </c>
+      <c r="F95" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>7</v>
+      </c>
+      <c r="B96" t="s">
+        <v>8</v>
+      </c>
+      <c r="C96" t="s">
+        <v>28</v>
+      </c>
+      <c r="D96" t="s">
+        <v>29</v>
+      </c>
+      <c r="E96" t="s">
+        <v>21</v>
+      </c>
+      <c r="F96" t="s">
+        <v>30</v>
+      </c>
+      <c r="G96" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>7</v>
+      </c>
+      <c r="B97" t="s">
+        <v>8</v>
+      </c>
+      <c r="C97" t="s">
+        <v>9</v>
+      </c>
+      <c r="D97" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" t="s">
+        <v>11</v>
+      </c>
+      <c r="F97" t="s">
+        <v>12</v>
+      </c>
+      <c r="G97" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>7</v>
+      </c>
+      <c r="B98" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98" t="s">
+        <v>15</v>
+      </c>
+      <c r="E98" t="s">
+        <v>16</v>
+      </c>
+      <c r="F98" t="s">
+        <v>17</v>
+      </c>
+      <c r="G98" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" t="s">
+        <v>19</v>
+      </c>
+      <c r="D99" t="s">
+        <v>20</v>
+      </c>
+      <c r="E99" t="s">
+        <v>21</v>
+      </c>
+      <c r="F99" t="s">
+        <v>22</v>
+      </c>
+      <c r="G99" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>7</v>
+      </c>
+      <c r="B100" t="s">
+        <v>8</v>
+      </c>
+      <c r="C100" t="s">
+        <v>24</v>
+      </c>
+      <c r="D100" t="s">
+        <v>25</v>
+      </c>
+      <c r="E100" t="s">
+        <v>21</v>
+      </c>
+      <c r="F100" t="s">
+        <v>26</v>
+      </c>
+      <c r="G100" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>7</v>
+      </c>
+      <c r="B101" t="s">
+        <v>8</v>
+      </c>
+      <c r="C101" t="s">
+        <v>28</v>
+      </c>
+      <c r="D101" t="s">
+        <v>29</v>
+      </c>
+      <c r="E101" t="s">
+        <v>21</v>
+      </c>
+      <c r="F101" t="s">
+        <v>30</v>
+      </c>
+      <c r="G101" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>